--- a/uploads/products.xlsx
+++ b/uploads/products.xlsx
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>68b85c66771ae9a18bc053b5</v>
+        <v>69fecdb330aa8eb88a2dc645</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>4000</v>
       </c>
       <c r="C2" t="str">
-        <v>f1</v>
+        <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>Oppo</v>
+        <v>test</v>
       </c>
       <c r="E2" t="str">
-        <v>ขาว</v>
+        <v>ดำ</v>
       </c>
       <c r="F2">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="G2" t="str">
-        <v>กิล</v>
+        <v>-</v>
       </c>
       <c r="H2" t="str">
-        <v>0971037598</v>
+        <v>0987567898</v>
       </c>
       <c r="I2" t="str">
-        <v>23/7</v>
+        <v>1/1</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -471,31 +471,31 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>68b85c65771ae9a18bc053b4</v>
+        <v>68c438aa9e705ffcce8a7030</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>3000</v>
       </c>
       <c r="C3" t="str">
-        <v>f1</v>
+        <v>17pro</v>
       </c>
       <c r="D3" t="str">
-        <v>Oppo</v>
+        <v>iphone</v>
       </c>
       <c r="E3" t="str">
-        <v>ขาว</v>
+        <v>ส้ม</v>
       </c>
       <c r="F3">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="G3" t="str">
-        <v>กิล</v>
+        <v>กร</v>
       </c>
       <c r="H3" t="str">
-        <v>0971037598</v>
+        <v>0964758965</v>
       </c>
       <c r="I3" t="str">
-        <v>23/7</v>
+        <v>23</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>68b85c65771ae9a18bc053b3</v>
+        <v>68b85c66771ae9a18bc053b9</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>68b85c65771ae9a18bc053b2</v>
+        <v>68b85c66771ae9a18bc053b8</v>
       </c>
       <c r="B5" t="str">
         <v/>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>68b85c65771ae9a18bc053b1</v>
+        <v>68b85c66771ae9a18bc053b7</v>
       </c>
       <c r="B6" t="str">
         <v/>
